--- a/data_lake/datos_diarios_preliminares/dt=2026-09-11/Temp-max-septiembre-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-09-11/Temp-max-septiembre-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.187.8\Oficina\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52ADE4DA-24F8-4E02-A55D-6D6C39FE22F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155DDFFD-C428-43C1-A4E9-C9F1F033F478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9450,7 +9450,9 @@
       <c r="M5" s="63">
         <v>32.1</v>
       </c>
-      <c r="N5" s="63"/>
+      <c r="N5" s="63">
+        <v>32.200000000000003</v>
+      </c>
       <c r="O5" s="63"/>
       <c r="P5" s="63"/>
       <c r="Q5" s="63"/>
@@ -9474,7 +9476,7 @@
       <c r="AI5" s="63"/>
       <c r="AJ5" s="36">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>32.1</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9541,7 +9543,9 @@
       <c r="M6" s="63">
         <v>32.6</v>
       </c>
-      <c r="N6" s="63"/>
+      <c r="N6" s="63">
+        <v>32.4</v>
+      </c>
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
@@ -9565,7 +9569,7 @@
       <c r="AI6" s="63"/>
       <c r="AJ6" s="36">
         <f t="shared" ref="AJ6:AJ48" si="1">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="2">+MAX($E6:$AI6)</f>
@@ -9632,7 +9636,9 @@
       <c r="M7" s="63">
         <v>36.9</v>
       </c>
-      <c r="N7" s="63"/>
+      <c r="N7" s="63">
+        <v>34.4</v>
+      </c>
       <c r="O7" s="63"/>
       <c r="P7" s="63"/>
       <c r="Q7" s="63"/>
@@ -9656,7 +9662,7 @@
       <c r="AI7" s="63"/>
       <c r="AJ7" s="36">
         <f t="shared" si="1"/>
-        <v>36.9</v>
+        <v>34.4</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="2"/>
@@ -9723,7 +9729,9 @@
       <c r="M8" s="63">
         <v>35.5</v>
       </c>
-      <c r="N8" s="63"/>
+      <c r="N8" s="63">
+        <v>34.1</v>
+      </c>
       <c r="O8" s="63"/>
       <c r="P8" s="63"/>
       <c r="Q8" s="63"/>
@@ -9747,7 +9755,7 @@
       <c r="AI8" s="63"/>
       <c r="AJ8" s="36">
         <f t="shared" si="1"/>
-        <v>35.5</v>
+        <v>34.1</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="2"/>
@@ -9814,7 +9822,9 @@
       <c r="M9" s="63">
         <v>36.1</v>
       </c>
-      <c r="N9" s="63"/>
+      <c r="N9" s="63">
+        <v>35.700000000000003</v>
+      </c>
       <c r="O9" s="63"/>
       <c r="P9" s="63"/>
       <c r="Q9" s="63"/>
@@ -9838,7 +9848,7 @@
       <c r="AI9" s="63"/>
       <c r="AJ9" s="36">
         <f t="shared" si="1"/>
-        <v>36.1</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="2"/>
@@ -9905,7 +9915,9 @@
       <c r="M10" s="63">
         <v>37.9</v>
       </c>
-      <c r="N10" s="63"/>
+      <c r="N10" s="63">
+        <v>38.200000000000003</v>
+      </c>
       <c r="O10" s="63"/>
       <c r="P10" s="63"/>
       <c r="Q10" s="63"/>
@@ -9929,7 +9941,7 @@
       <c r="AI10" s="63"/>
       <c r="AJ10" s="36">
         <f t="shared" si="1"/>
-        <v>37.9</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="2"/>
@@ -9996,7 +10008,9 @@
       <c r="M11" s="63">
         <v>39.799999999999997</v>
       </c>
-      <c r="N11" s="63"/>
+      <c r="N11" s="63">
+        <v>37.700000000000003</v>
+      </c>
       <c r="O11" s="63"/>
       <c r="P11" s="63"/>
       <c r="Q11" s="63"/>
@@ -10020,7 +10034,7 @@
       <c r="AI11" s="63"/>
       <c r="AJ11" s="36">
         <f t="shared" si="1"/>
-        <v>39.799999999999997</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="2"/>
@@ -10087,7 +10101,9 @@
       <c r="M12" s="63">
         <v>36.6</v>
       </c>
-      <c r="N12" s="63"/>
+      <c r="N12" s="63">
+        <v>35.200000000000003</v>
+      </c>
       <c r="O12" s="63"/>
       <c r="P12" s="63"/>
       <c r="Q12" s="63"/>
@@ -10111,7 +10127,7 @@
       <c r="AI12" s="63"/>
       <c r="AJ12" s="36">
         <f t="shared" si="1"/>
-        <v>36.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="2"/>
@@ -10178,7 +10194,9 @@
       <c r="M13" s="63">
         <v>37.200000000000003</v>
       </c>
-      <c r="N13" s="63"/>
+      <c r="N13" s="63">
+        <v>36.799999999999997</v>
+      </c>
       <c r="O13" s="63"/>
       <c r="P13" s="63"/>
       <c r="Q13" s="63"/>
@@ -10202,7 +10220,7 @@
       <c r="AI13" s="63"/>
       <c r="AJ13" s="36">
         <f t="shared" si="1"/>
-        <v>37.200000000000003</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="2"/>
@@ -10269,7 +10287,9 @@
       <c r="M14" s="63">
         <v>36.4</v>
       </c>
-      <c r="N14" s="63"/>
+      <c r="N14" s="63">
+        <v>33.4</v>
+      </c>
       <c r="O14" s="63"/>
       <c r="P14" s="63"/>
       <c r="Q14" s="63"/>
@@ -10293,7 +10313,7 @@
       <c r="AI14" s="63"/>
       <c r="AJ14" s="36">
         <f t="shared" si="1"/>
-        <v>36.4</v>
+        <v>33.4</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="2"/>
@@ -10360,7 +10380,9 @@
       <c r="M15" s="63">
         <v>32.299999999999997</v>
       </c>
-      <c r="N15" s="63"/>
+      <c r="N15" s="63">
+        <v>33.200000000000003</v>
+      </c>
       <c r="O15" s="63"/>
       <c r="P15" s="63"/>
       <c r="Q15" s="63"/>
@@ -10384,7 +10406,7 @@
       <c r="AI15" s="63"/>
       <c r="AJ15" s="36">
         <f t="shared" si="1"/>
-        <v>32.299999999999997</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="2"/>
@@ -10500,7 +10522,9 @@
       <c r="M17" s="63">
         <v>37.6</v>
       </c>
-      <c r="N17" s="63"/>
+      <c r="N17" s="63">
+        <v>35.799999999999997</v>
+      </c>
       <c r="O17" s="63"/>
       <c r="P17" s="63"/>
       <c r="Q17" s="63"/>
@@ -10524,7 +10548,7 @@
       <c r="AI17" s="63"/>
       <c r="AJ17" s="36">
         <f t="shared" si="1"/>
-        <v>37.6</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="2"/>
@@ -10591,7 +10615,9 @@
       <c r="M18" s="63">
         <v>29.6</v>
       </c>
-      <c r="N18" s="63"/>
+      <c r="N18" s="63">
+        <v>30.2</v>
+      </c>
       <c r="O18" s="63"/>
       <c r="P18" s="63"/>
       <c r="Q18" s="63"/>
@@ -10615,7 +10641,7 @@
       <c r="AI18" s="63"/>
       <c r="AJ18" s="36">
         <f t="shared" si="1"/>
-        <v>29.6</v>
+        <v>30.2</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="2"/>
@@ -10682,7 +10708,9 @@
       <c r="M19" s="63">
         <v>35.4</v>
       </c>
-      <c r="N19" s="63"/>
+      <c r="N19" s="63">
+        <v>35.200000000000003</v>
+      </c>
       <c r="O19" s="63"/>
       <c r="P19" s="63"/>
       <c r="Q19" s="63"/>
@@ -10706,7 +10734,7 @@
       <c r="AI19" s="63"/>
       <c r="AJ19" s="36">
         <f t="shared" si="1"/>
-        <v>35.4</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="2"/>
@@ -10773,7 +10801,9 @@
       <c r="M20" s="63">
         <v>32.4</v>
       </c>
-      <c r="N20" s="63"/>
+      <c r="N20" s="63">
+        <v>32</v>
+      </c>
       <c r="O20" s="63"/>
       <c r="P20" s="63"/>
       <c r="Q20" s="63"/>
@@ -10797,7 +10827,7 @@
       <c r="AI20" s="63"/>
       <c r="AJ20" s="36">
         <f t="shared" si="1"/>
-        <v>32.4</v>
+        <v>32</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="2"/>
@@ -10864,7 +10894,9 @@
       <c r="M21" s="63">
         <v>25</v>
       </c>
-      <c r="N21" s="63"/>
+      <c r="N21" s="63">
+        <v>25.3</v>
+      </c>
       <c r="O21" s="63"/>
       <c r="P21" s="63"/>
       <c r="Q21" s="63"/>
@@ -10888,18 +10920,18 @@
       <c r="AI21" s="63"/>
       <c r="AJ21" s="36">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="AL21" s="22">
         <v>26.9</v>
       </c>
       <c r="AM21" s="23">
         <f t="shared" si="3"/>
-        <v>-1.8999999999999986</v>
+        <v>-1.5999999999999979</v>
       </c>
       <c r="AN21" s="23">
         <v>22.564435196194999</v>
@@ -11021,7 +11053,9 @@
       <c r="M23" s="63">
         <v>30.6</v>
       </c>
-      <c r="N23" s="63"/>
+      <c r="N23" s="63">
+        <v>30.8</v>
+      </c>
       <c r="O23" s="63"/>
       <c r="P23" s="63"/>
       <c r="Q23" s="63"/>
@@ -11045,7 +11079,7 @@
       <c r="AI23" s="63"/>
       <c r="AJ23" s="36">
         <f t="shared" si="1"/>
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="2"/>
@@ -11112,7 +11146,9 @@
       <c r="M24" s="63">
         <v>31.7</v>
       </c>
-      <c r="N24" s="63"/>
+      <c r="N24" s="63">
+        <v>31.7</v>
+      </c>
       <c r="O24" s="63"/>
       <c r="P24" s="63"/>
       <c r="Q24" s="63"/>
@@ -11203,7 +11239,9 @@
       <c r="M25" s="63">
         <v>35.4</v>
       </c>
-      <c r="N25" s="63"/>
+      <c r="N25" s="63">
+        <v>36</v>
+      </c>
       <c r="O25" s="63"/>
       <c r="P25" s="63"/>
       <c r="Q25" s="63"/>
@@ -11227,18 +11265,18 @@
       <c r="AI25" s="63"/>
       <c r="AJ25" s="36">
         <f t="shared" si="1"/>
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="2"/>
-        <v>35.799999999999997</v>
+        <v>36</v>
       </c>
       <c r="AL25" s="22">
         <v>36.799999999999997</v>
       </c>
       <c r="AM25" s="23">
         <f t="shared" si="3"/>
-        <v>-1</v>
+        <v>-0.79999999999999716</v>
       </c>
       <c r="AN25" s="23">
         <v>30.83648877941982</v>
@@ -11294,7 +11332,9 @@
       <c r="M26" s="63">
         <v>21.4</v>
       </c>
-      <c r="N26" s="63"/>
+      <c r="N26" s="63">
+        <v>21</v>
+      </c>
       <c r="O26" s="63"/>
       <c r="P26" s="63"/>
       <c r="Q26" s="63"/>
@@ -11318,7 +11358,7 @@
       <c r="AI26" s="63"/>
       <c r="AJ26" s="36">
         <f t="shared" si="1"/>
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="2"/>
@@ -11385,7 +11425,9 @@
       <c r="M27" s="63">
         <v>21.8</v>
       </c>
-      <c r="N27" s="63"/>
+      <c r="N27" s="63">
+        <v>22</v>
+      </c>
       <c r="O27" s="63"/>
       <c r="P27" s="63"/>
       <c r="Q27" s="63"/>
@@ -11409,18 +11451,18 @@
       <c r="AI27" s="63"/>
       <c r="AJ27" s="36">
         <f t="shared" si="1"/>
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="2"/>
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AL27" s="22">
         <v>23.4</v>
       </c>
       <c r="AM27" s="23">
         <f t="shared" si="3"/>
-        <v>-1.5999999999999979</v>
+        <v>-1.3999999999999986</v>
       </c>
       <c r="AN27" s="23">
         <v>18.093990147783249</v>
@@ -11476,7 +11518,9 @@
       <c r="M28" s="63">
         <v>34.799999999999997</v>
       </c>
-      <c r="N28" s="63"/>
+      <c r="N28" s="63">
+        <v>34.5</v>
+      </c>
       <c r="O28" s="63"/>
       <c r="P28" s="63"/>
       <c r="Q28" s="63"/>
@@ -11500,7 +11544,7 @@
       <c r="AI28" s="63"/>
       <c r="AJ28" s="36">
         <f t="shared" si="1"/>
-        <v>34.799999999999997</v>
+        <v>34.5</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="2"/>
@@ -11631,7 +11675,9 @@
       <c r="M30" s="63">
         <v>38.200000000000003</v>
       </c>
-      <c r="N30" s="63"/>
+      <c r="N30" s="63">
+        <v>35.6</v>
+      </c>
       <c r="O30" s="63"/>
       <c r="P30" s="63"/>
       <c r="Q30" s="63"/>
@@ -11655,7 +11701,7 @@
       <c r="AI30" s="63"/>
       <c r="AJ30" s="36">
         <f t="shared" si="1"/>
-        <v>38.200000000000003</v>
+        <v>35.6</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="2"/>
@@ -11722,7 +11768,9 @@
       <c r="M31" s="63">
         <v>27.8</v>
       </c>
-      <c r="N31" s="63"/>
+      <c r="N31" s="63">
+        <v>29.8</v>
+      </c>
       <c r="O31" s="63"/>
       <c r="P31" s="63"/>
       <c r="Q31" s="63"/>
@@ -11746,18 +11794,18 @@
       <c r="AI31" s="63"/>
       <c r="AJ31" s="36">
         <f t="shared" si="1"/>
-        <v>27.8</v>
+        <v>29.8</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="2"/>
-        <v>28.4</v>
+        <v>29.8</v>
       </c>
       <c r="AL31" s="22">
         <v>31.2</v>
       </c>
       <c r="AM31" s="23">
         <f t="shared" si="3"/>
-        <v>-2.8000000000000007</v>
+        <v>-1.3999999999999986</v>
       </c>
       <c r="AN31" s="23">
         <v>25.982387369533619</v>
@@ -11813,7 +11861,9 @@
       <c r="M32" s="63">
         <v>18.8</v>
       </c>
-      <c r="N32" s="63"/>
+      <c r="N32" s="63">
+        <v>21</v>
+      </c>
       <c r="O32" s="63"/>
       <c r="P32" s="63"/>
       <c r="Q32" s="63"/>
@@ -11837,7 +11887,7 @@
       <c r="AI32" s="63"/>
       <c r="AJ32" s="36">
         <f t="shared" si="1"/>
-        <v>18.8</v>
+        <v>21</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="2"/>
@@ -11904,7 +11954,9 @@
       <c r="M33" s="63">
         <v>16.399999999999999</v>
       </c>
-      <c r="N33" s="63"/>
+      <c r="N33" s="63">
+        <v>17.8</v>
+      </c>
       <c r="O33" s="63"/>
       <c r="P33" s="63"/>
       <c r="Q33" s="63"/>
@@ -11928,7 +11980,7 @@
       <c r="AI33" s="63"/>
       <c r="AJ33" s="36">
         <f t="shared" si="1"/>
-        <v>16.399999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="2"/>
@@ -12047,7 +12099,9 @@
       <c r="M35" s="63">
         <v>31</v>
       </c>
-      <c r="N35" s="63"/>
+      <c r="N35" s="63">
+        <v>33.4</v>
+      </c>
       <c r="O35" s="63"/>
       <c r="P35" s="63"/>
       <c r="Q35" s="63"/>
@@ -12071,7 +12125,7 @@
       <c r="AI35" s="63"/>
       <c r="AJ35" s="36">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>33.4</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="2"/>
@@ -12257,7 +12311,9 @@
       <c r="M38" s="63">
         <v>33.5</v>
       </c>
-      <c r="N38" s="63"/>
+      <c r="N38" s="63">
+        <v>32.4</v>
+      </c>
       <c r="O38" s="63"/>
       <c r="P38" s="63"/>
       <c r="Q38" s="63"/>
@@ -12281,7 +12337,7 @@
       <c r="AI38" s="63"/>
       <c r="AJ38" s="36">
         <f t="shared" si="1"/>
-        <v>33.5</v>
+        <v>32.4</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="2"/>
@@ -12349,7 +12405,9 @@
       <c r="M39" s="63">
         <v>34.799999999999997</v>
       </c>
-      <c r="N39" s="63"/>
+      <c r="N39" s="63">
+        <v>32.4</v>
+      </c>
       <c r="O39" s="63"/>
       <c r="P39" s="63"/>
       <c r="Q39" s="63"/>
@@ -12373,7 +12431,7 @@
       <c r="AI39" s="63"/>
       <c r="AJ39" s="36">
         <f t="shared" si="1"/>
-        <v>34.799999999999997</v>
+        <v>32.4</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="2"/>
@@ -12441,7 +12499,9 @@
       <c r="M40" s="63">
         <v>31.7</v>
       </c>
-      <c r="N40" s="63"/>
+      <c r="N40" s="63">
+        <v>31</v>
+      </c>
       <c r="O40" s="63"/>
       <c r="P40" s="63"/>
       <c r="Q40" s="63"/>
@@ -12465,7 +12525,7 @@
       <c r="AI40" s="63"/>
       <c r="AJ40" s="36">
         <f t="shared" si="1"/>
-        <v>31.7</v>
+        <v>31</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="2"/>
@@ -12533,7 +12593,9 @@
       <c r="M41" s="63">
         <v>32.799999999999997</v>
       </c>
-      <c r="N41" s="63"/>
+      <c r="N41" s="63">
+        <v>29</v>
+      </c>
       <c r="O41" s="63"/>
       <c r="P41" s="63"/>
       <c r="Q41" s="63"/>
@@ -12557,7 +12619,7 @@
       <c r="AI41" s="63"/>
       <c r="AJ41" s="36">
         <f t="shared" si="1"/>
-        <v>32.799999999999997</v>
+        <v>29</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="2"/>
@@ -12693,7 +12755,9 @@
       <c r="M43" s="63">
         <v>33.4</v>
       </c>
-      <c r="N43" s="63"/>
+      <c r="N43" s="63">
+        <v>30.6</v>
+      </c>
       <c r="O43" s="63"/>
       <c r="P43" s="63"/>
       <c r="Q43" s="63"/>
@@ -12717,7 +12781,7 @@
       <c r="AI43" s="63"/>
       <c r="AJ43" s="36">
         <f t="shared" si="1"/>
-        <v>33.4</v>
+        <v>30.6</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="2"/>
@@ -12785,7 +12849,9 @@
       <c r="M44" s="29">
         <v>33.1</v>
       </c>
-      <c r="N44" s="29"/>
+      <c r="N44" s="29">
+        <v>31.4</v>
+      </c>
       <c r="O44" s="29"/>
       <c r="P44" s="29"/>
       <c r="Q44" s="29"/>
@@ -12809,7 +12875,7 @@
       <c r="AI44" s="63"/>
       <c r="AJ44" s="36">
         <f t="shared" si="1"/>
-        <v>33.1</v>
+        <v>31.4</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="2"/>
@@ -12877,7 +12943,9 @@
       <c r="M45" s="63">
         <v>31.6</v>
       </c>
-      <c r="N45" s="63"/>
+      <c r="N45" s="63">
+        <v>27.4</v>
+      </c>
       <c r="O45" s="63"/>
       <c r="P45" s="63"/>
       <c r="Q45" s="63"/>
@@ -12901,7 +12969,7 @@
       <c r="AI45" s="63"/>
       <c r="AJ45" s="36">
         <f t="shared" si="1"/>
-        <v>31.6</v>
+        <v>27.4</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="2"/>
@@ -13101,7 +13169,9 @@
       <c r="M48" s="63">
         <v>32.9</v>
       </c>
-      <c r="N48" s="63"/>
+      <c r="N48" s="63">
+        <v>33.299999999999997</v>
+      </c>
       <c r="O48" s="63"/>
       <c r="P48" s="63"/>
       <c r="Q48" s="63"/>
@@ -13125,7 +13195,7 @@
       <c r="AI48" s="63"/>
       <c r="AJ48" s="36">
         <f t="shared" si="1"/>
-        <v>32.9</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="2"/>
@@ -26203,12 +26273,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -26218,6 +26282,12 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
